--- a/pensum/ma03/MA03_Markedsplanen_Regneark_Markedsbudsjett.xlsx
+++ b/pensum/ma03/MA03_Markedsplanen_Regneark_Markedsbudsjett.xlsx
@@ -1024,7 +1024,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1159,6 +1159,10 @@
     </xf>
     <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1515,7 +1519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -1857,8 +1861,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row ht="27" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="34" r="A30" t="s">
         <v>73</v>
       </c>
       <c r="B30" s="21" t="s">
@@ -2466,8 +2470,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row ht="27" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="34" r="A14" t="s">
         <v>157</v>
       </c>
       <c r="B14" s="30" t="n">
